--- a/BimManagement/BimManagement/Commands/CreateReportSheet/Resources/Partidas/UT7/UT7-ARQ.xlsx
+++ b/BimManagement/BimManagement/Commands/CreateReportSheet/Resources/Partidas/UT7/UT7-ARQ.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Developer\cesel-audit-models\BimManagement\BimManagement\Commands\CreateReportSheet\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProgramData\Autodesk\Revit\Addins\2024\CESEL\Resources\Partidas\UT7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF725EE-C6F8-4274-8705-E1340ADAE48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B079D5-1AEE-4E41-9BAE-46982603D5DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BE9C153A-9620-42B3-B70E-62F7CFA0BB10}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{BE9C153A-9620-42B3-B70E-62F7CFA0BB10}"/>
   </bookViews>
   <sheets>
     <sheet name="UT7" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="275">
   <si>
     <t>und</t>
   </si>
@@ -62,716 +63,812 @@
     <t>03.01.01</t>
   </si>
   <si>
-    <t xml:space="preserve">    MUROS Y TABIQUES DE ALBAÑILERIA</t>
-  </si>
-  <si>
     <t>03.01.01.01</t>
   </si>
   <si>
-    <t xml:space="preserve">        MUROS DE LADRILLO KING KONG DE ARCILLA</t>
-  </si>
-  <si>
     <t>03.01.01.01.01</t>
   </si>
   <si>
-    <t xml:space="preserve">            MURO LADRILLO KK TIPO IV MEZCLA 1:5, JUNTAS 1.5cm DE SOGA</t>
-  </si>
-  <si>
     <t>03.01.01.02</t>
   </si>
   <si>
-    <t xml:space="preserve">        MUROS DE LADRILLO CALCAREO</t>
-  </si>
-  <si>
     <t>03.01.01.02.01</t>
   </si>
   <si>
-    <t xml:space="preserve">            MURO LADRILLO SILICO CALCAREO MEZCLA 1:5, JUNTAS 1.5cm DE SOGA</t>
-  </si>
-  <si>
     <t>03.01.01.03</t>
   </si>
   <si>
-    <t xml:space="preserve">        MUROS CON EL SISTEMA DE CONSTRUCCION EN SECO (SISTEMA DRYWALL O SIMILAR)</t>
-  </si>
-  <si>
     <t>03.01.01.03.01</t>
   </si>
   <si>
-    <t xml:space="preserve">            TABIQUERIA DE DRYWALL INCLUYE PARANTES Y RIELES</t>
-  </si>
-  <si>
     <t>03.01.01.03.02</t>
   </si>
   <si>
-    <t xml:space="preserve">            TABIQUERIA DE DRYWALL RESISTENTE AL FUEGO INCLUYE RIELES Y PARANTES</t>
-  </si>
-  <si>
     <t>03.01.01.03.03</t>
   </si>
   <si>
-    <t xml:space="preserve">            VIGAS DE FIBROCEMENTO INCLUYE RIELES Y PARANTES</t>
-  </si>
-  <si>
     <t>03.01.02</t>
   </si>
   <si>
-    <t xml:space="preserve">    REVOQUES Y REVESTIMIENTOS</t>
-  </si>
-  <si>
     <t>03.01.02.01</t>
   </si>
   <si>
-    <t xml:space="preserve">        TARRAJEO RAYADO PRIMARIO</t>
-  </si>
-  <si>
     <t>03.01.02.01.01</t>
   </si>
   <si>
-    <t xml:space="preserve">            TARRAJEO PRIMARIO Y RAYADO C/ MEZCLA 1:5 E=1.5cm</t>
-  </si>
-  <si>
     <t>03.01.02.02</t>
   </si>
   <si>
-    <t xml:space="preserve">        TARRAJEO EN INTERIORES</t>
-  </si>
-  <si>
     <t>03.01.02.02.01</t>
   </si>
   <si>
-    <t xml:space="preserve">            TARRAJEO DE MUROS INTERIORES FROTACHADO CON MEZ. C:A 1:5, E=1.5cm</t>
-  </si>
-  <si>
     <t>03.01.02.02.02</t>
   </si>
   <si>
-    <t xml:space="preserve">            TARRAJEO DE PLACAS MEZ. C:A 1:5, E=1.5cm.</t>
-  </si>
-  <si>
     <t>03.01.02.02.03</t>
   </si>
   <si>
-    <t xml:space="preserve">            TARRAJEO DE COLUMNAS MEZ. C:A 1:5, E=1.5 CM.</t>
-  </si>
-  <si>
     <t>03.01.02.02.04</t>
   </si>
   <si>
-    <t xml:space="preserve">            TARRAJEO DE VIGAS MEZLA C:A 1:5, E=1.5 CM.</t>
-  </si>
-  <si>
     <t>03.01.02.03</t>
   </si>
   <si>
-    <t xml:space="preserve">        TARRAJEO EN EXTERIORES</t>
-  </si>
-  <si>
     <t>03.01.02.03.01</t>
   </si>
   <si>
-    <t xml:space="preserve">            TARRAJEO DE MUROS EXTERIORES, MEZCLA C:A 1:5, E=1.5cm</t>
-  </si>
-  <si>
     <t>03.01.02.04</t>
   </si>
   <si>
-    <t xml:space="preserve">        VESTIDURA DE DERRAMES</t>
-  </si>
-  <si>
     <t>03.01.02.04.01</t>
   </si>
   <si>
-    <t xml:space="preserve">            VESTIDURA DE DERRAMES A=0.15m, MEZCLA C:A 1:5 E=1.5cm</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
     <t>03.01.02.05</t>
   </si>
   <si>
-    <t xml:space="preserve">        BRUÑAS</t>
-  </si>
-  <si>
     <t>03.01.02.05.01</t>
   </si>
   <si>
-    <t xml:space="preserve">            BRUÑAS 1cm x 1cm</t>
-  </si>
-  <si>
     <t>03.01.02.06</t>
   </si>
   <si>
-    <t xml:space="preserve">        TARRAJEO EN FONDO DE ESCALERA</t>
-  </si>
-  <si>
     <t>03.01.02.06.01</t>
   </si>
   <si>
-    <t xml:space="preserve">            TARRAJEO EN FONDO EN ESCALERA, E=1.5cm. C:A 1:5</t>
-  </si>
-  <si>
     <t>03.01.02.07</t>
   </si>
   <si>
-    <t xml:space="preserve">        REVESTIMIENTOS</t>
-  </si>
-  <si>
     <t>03.01.02.07.01</t>
   </si>
   <si>
-    <t xml:space="preserve">            REVESTIMIENTO DE TABLERO DE CONCRETO CON CERAMICO 0.30X0.30m				</t>
-  </si>
-  <si>
-    <t>03.01.02.07.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            REVESTIMIENTO DE SARDINEL CON CERAMICO ANTIDESLIZANTE 0.30x0.30m</t>
-  </si>
-  <si>
     <t>03.01.02.07.03</t>
   </si>
   <si>
-    <t xml:space="preserve">            VESTIDURA DE FONDO DE TABLERO</t>
-  </si>
-  <si>
     <t>03.01.02.07.04</t>
   </si>
   <si>
-    <t xml:space="preserve">            REVESTIMIENTO DE CEMENTO SEMIPULIDO EN BANCA DE CONCRETO</t>
-  </si>
-  <si>
     <t>03.01.03</t>
   </si>
   <si>
-    <t xml:space="preserve">    CIELORRASOS</t>
-  </si>
-  <si>
     <t>03.01.03.01</t>
   </si>
   <si>
-    <t xml:space="preserve">        FALSO CIELORRASO</t>
-  </si>
-  <si>
-    <t>03.01.03.01.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            FALSO CIELO RASO CON BALDOSA  RESISTENTE A LA HUMEDAD DE 0.60mx0.60m.</t>
-  </si>
-  <si>
     <t>03.01.04</t>
   </si>
   <si>
-    <t xml:space="preserve">    PISOS Y PAVIMENTOS</t>
-  </si>
-  <si>
     <t>03.01.04.01</t>
   </si>
   <si>
-    <t xml:space="preserve">        CONTRAPISOS</t>
-  </si>
-  <si>
-    <t>03.01.04.01.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            CONTRAPISO DE CEMENTO 37mm, MEZCLA 1:5</t>
-  </si>
-  <si>
     <t>03.01.04.02</t>
   </si>
   <si>
-    <t xml:space="preserve">        PISOS</t>
-  </si>
-  <si>
     <t>03.01.04.02.02</t>
   </si>
   <si>
-    <t xml:space="preserve">            PISOS DE CERAMICO</t>
-  </si>
-  <si>
     <t>03.01.04.02.02.01</t>
   </si>
   <si>
-    <t xml:space="preserve">                PISO DE CERAMICO ALTO TRANSITO PEI-IV, 30cm x 30cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            PISOS EN PISTA ATLETICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                CONFORMACION Y COMPACTACION A NIVEL DE SUBRASANTE C/EQUIPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                BASE GRANULAR e=0.20 m.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                IMPRIMACION ASFALTICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                CARPETA ASFALTICA EN CALIENTE e = 2"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                RIEGO DE LIGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                CARPETA ASFALTICA EN CALIENTE e=3cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                PISTA ATLETICA SISTEMA SPRAY e=13mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                DEMARCACION DE PISTA ATLETICA</t>
-  </si>
-  <si>
-    <t>04.00.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            PISOS DE GRASS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                PREPARACION DE TERRENO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                NIVELACION A NIVEL DE RASANTE C/MAQ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                COMPACTADO CON RODILLO MANUAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                SIEMBRA DE GRAS BERMUDA INC RASTRILLADO Y RULADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                FERTILIZACION DEL SUELO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                MANTENIMIENTO DE GRAS POR 30 DIAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                PINTURA  DE DEMARCACION EN CAMPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                REFINE Y NIVELADO DE TERRENO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                SEMBRADO DE GRASS INC. TIERRA DE CHACRA</t>
-  </si>
-  <si>
     <t>03.01.04.02.04</t>
   </si>
   <si>
-    <t xml:space="preserve">            PISOS DE CEMENTO</t>
-  </si>
-  <si>
     <t>03.01.04.02.04.01</t>
   </si>
   <si>
-    <t xml:space="preserve">                PISO DE CEMENTO PULIDO Y BRUÑADO @1m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                VEREDA DE CONCRETO F'C=175 KG/CM2 E=0.10M EN VEREDA, ACABADO SEMIPULIDO CON BRUÑAS @1.00 m</t>
-  </si>
-  <si>
     <t>03.01.04.02.05</t>
   </si>
   <si>
-    <t xml:space="preserve">            SARDINELES</t>
-  </si>
-  <si>
     <t>03.01.04.02.05.01</t>
   </si>
   <si>
-    <t xml:space="preserve">                SARDINEL DE CONCRETO PARA DUCHAS (ANCHO=0.08m, ALTURA=0.10m)</t>
-  </si>
-  <si>
     <t>03.01.05</t>
   </si>
   <si>
-    <t xml:space="preserve">    ZOCALOS Y CONTRAZOCALOS</t>
-  </si>
-  <si>
     <t>03.01.05.01</t>
   </si>
   <si>
-    <t xml:space="preserve">        ZOCALOS</t>
-  </si>
-  <si>
-    <t>03.01.05.01.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            ZOCALO DE CERAMICO</t>
-  </si>
-  <si>
-    <t>03.01.05.01.02.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                ZOCALO DE CERAMICO 30cm x 30cm, h=1.80m</t>
-  </si>
-  <si>
     <t>03.01.05.02</t>
   </si>
   <si>
-    <t xml:space="preserve">        CONTRAZOCALOS</t>
-  </si>
-  <si>
-    <t>03.01.05.02.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            CONTRAZOCALO DE CEMENTO</t>
-  </si>
-  <si>
-    <t>03.01.05.02.02.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                CONTRAZOCALO DE CEMENTO PULIDO; H = 0.10m, MEZCLA 1:5</t>
-  </si>
-  <si>
     <t>03.01.07</t>
   </si>
   <si>
-    <t xml:space="preserve">    CARPINTERIA DE MADERA</t>
-  </si>
-  <si>
     <t>03.01.07.01</t>
   </si>
   <si>
-    <t xml:space="preserve">        PUERTAS DE MADERA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            PUERTA APANELADA  MADERA TORNILLO 2"x5", (1 HOJA); INC MARCO  Y ACC FIJACION, B08-PA01 (1.00mx2.60m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            PUERTA APANELADA  MADERA TORNILLO 2"x5", (1 HOJA); INC MARCO  Y ACC FIJACION, B08-PA02 (0.90mx2.60m)</t>
-  </si>
-  <si>
     <t>03.01.07.02</t>
   </si>
   <si>
-    <t xml:space="preserve">        DIVISIONES PARA SERVICIOS HIGIENICOS</t>
-  </si>
-  <si>
     <t>03.01.07.02.01</t>
   </si>
   <si>
-    <t xml:space="preserve">            DIVISIONES DE TABLERO MELAMINICO e= 18 mm EN SS.HH.; INCL. ESTRUCTURA DE TUBULAR DE ALUMINIO 1 1/2" X 1 1/2" Y ACC H=1.80m, INCLUYE PUERTAS Y ACCESORIOS.</t>
-  </si>
-  <si>
-    <t>03.01.07.02.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            DIVISIONES DE TABLERO MELAMINICO e= 18 mm EN URINARIOS.; INCL. ACCESORIOS L=0.40m, H=0.75m</t>
-  </si>
-  <si>
     <t>03.01.08</t>
   </si>
   <si>
-    <t xml:space="preserve">    CARPINTERIA METALICA Y HERRERIA</t>
-  </si>
-  <si>
     <t>03.01.08.01</t>
   </si>
   <si>
-    <t xml:space="preserve">        PUERTAS METALICAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            PUERTA DE ACERO GALV. C/MARCO, CERTIFICACION UL, ACC FIJACION (1 HOJA), B08-PCF01 (1.00mx2.10m)</t>
-  </si>
-  <si>
-    <t>03.01.08.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        VENTANAS DE ALUMINIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            VENTANA ALTA DE ALUMINIO SISTEMA PIVOT, CON VIDRIO TEMPLADO INCOLORO DE 6mm, INC.ACCESORIOS</t>
-  </si>
-  <si>
-    <t>03.01.08.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        BARANDAS METALICAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            BARANDA DE TUBO DE FIERRO NEGRO Ø 2" e=1.5mm Y Ø 1" e=1.5mm, C/ PARANTE Ø 1 1/2" e=1.5mm, H = 1.00m, INC ACC Y ACAB SATINADO BASE ZINCROMATO, ANTICORROSIVO Y PINTURA ESMALTE</t>
-  </si>
-  <si>
-    <t>119229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        PASAMANOS METALICOS</t>
-  </si>
-  <si>
-    <t>0401/1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            PASAMANOS DE TUBO DE FIERRO NEGRO Ø 2" e=1.5mm, IN ACC Y ACAB SATINADO BASE ZINCROMATO, ANTICORROSIVO Y PINTURA ESMALTE</t>
-  </si>
-  <si>
-    <t>03.01.08.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        ELEMENTOS METALICOS ESPECIALES</t>
-  </si>
-  <si>
-    <t>03.01.08.06.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            PLATINA DE ALUMINIO EN CAMBIO DE ACABADOS DE PISO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            JAULA PARA LANZAMIENTO DE MARTILLO Y DISCO</t>
-  </si>
-  <si>
     <t>03.01.09</t>
   </si>
   <si>
-    <t xml:space="preserve">    CERRAJERIA</t>
-  </si>
-  <si>
     <t>03.01.09.01</t>
   </si>
   <si>
-    <t xml:space="preserve">        CERRADURAS</t>
-  </si>
-  <si>
     <t>03.01.09.01.01</t>
   </si>
   <si>
-    <t xml:space="preserve">            CERRADURA CON MANIJA TIPO PALANCA PARA PUERTAS DE MADERA CONTRAPLACADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            CERRADURA CERTIFICACION UL CON UN PUNTO DE CIERRE + MANIJA EXTERIOR E INTERIOR</t>
-  </si>
-  <si>
     <t>03.01.09.02</t>
   </si>
   <si>
-    <t xml:space="preserve">        BISAGRAS</t>
-  </si>
-  <si>
     <t>03.01.09.02.01</t>
   </si>
   <si>
-    <t xml:space="preserve">            BISAGRA T2- SET 4 BISAGRAS CAPUCHINAS ALUMINIZADAS 4"x4" INC TORNILLOS FIJACIÓN</t>
-  </si>
-  <si>
     <t>03.01.10</t>
   </si>
   <si>
-    <t xml:space="preserve">    PINTURA</t>
-  </si>
-  <si>
-    <t>190017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        PINTURA DE CIELORRASOS, VIGAS</t>
-  </si>
-  <si>
-    <t>060102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            PINTURA DE CIELORRASOS Y VIGAS CON IMPRIMANTE Y ACABADO LATEX (2 MANOS)</t>
-  </si>
-  <si>
-    <t>03.01.10.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        PINTURA DE MUROS INTERIORES, COLUMNAS, MUROS DE CONCRETO Y PLACAS</t>
-  </si>
-  <si>
-    <t>03.01.10.02.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            PINTURA DE MUROS INTERIORES CON IMPRIMANTE Y ACABADO LATEX (2 MANOS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            PINTURA DE MUROS DE DRYWALL O FIBROCEMENTO  ACABADO LATEX (2 MANOS)</t>
-  </si>
-  <si>
-    <t>03.01.10.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        PINTURA DE MUROS EXTERIORES</t>
-  </si>
-  <si>
-    <t>03.01.10.03.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            PINTURA DE MUROS EXTERIORES CON IMPRIMANTE Y ACABADO LATEX (2 MANOS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            PINTURA DE DERRAME CON IMPRIMANTE Y ACABADO LATEX (2 MANOS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        PINTURA VARIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            PINTURA EN PISO PARA SEÑAL DE DISCAPACITADOS Y SILLA C/PINTURA DE TRANSITO BLANCO 1.50x1.50m</t>
-  </si>
-  <si>
     <t>03.01.11</t>
   </si>
   <si>
-    <t xml:space="preserve">    VARIOS, LIMPIEZA, JARDINERIA</t>
-  </si>
-  <si>
     <t>03.01.11.01</t>
   </si>
   <si>
-    <t xml:space="preserve">        VARIOS</t>
-  </si>
-  <si>
-    <t>03.01.11.01.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            TABLERO DE CONCRETO e=0.08m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            JUNTAS DE CONSTRUCCION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SOLAQUEO LADO VERTICAL DE GRADERIAS</t>
-  </si>
-  <si>
-    <t>03.01.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    SEÑALIZACION Y SEGURIDAD</t>
-  </si>
-  <si>
-    <t>03.01.12.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        SEÑAL ORIENTATIVA - INDICATIVA</t>
-  </si>
-  <si>
-    <t>03.01.12.01.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            T.01 IDENTIFICATIVO ADOSADO DE 0.45mx0.60m</t>
-  </si>
-  <si>
-    <t>03.01.12.01.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            T.02 IDENTIFICATIVO ADOSADO DE 0.15mx0.30m</t>
-  </si>
-  <si>
-    <t>03.01.12.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        SEÑAL DE SEGURIDAD</t>
-  </si>
-  <si>
-    <t>03.01.12.02.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SEÑAL ACCESO DE SALIDA AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.30mx0.20m)</t>
-  </si>
-  <si>
-    <t>03.01.12.02.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SEÑAL DIRECCION EN SENTIDO DE EVACUACION AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 3mm (0.20mx0.30m)</t>
-  </si>
-  <si>
-    <t>03.01.12.02.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SEÑAL SUBIR-BAJAR ESCALERA AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.20mx0.30m)</t>
-  </si>
-  <si>
-    <t>03.01.12.02.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SEÑAL PUERTA CORTAFUEGO AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.20mx0.30m)</t>
-  </si>
-  <si>
-    <t>03.01.12.02.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SEÑAL EXTINTOR TIPO PQS AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.20mx0.30m)</t>
-  </si>
-  <si>
-    <t>03.01.12.02.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SEÑAL EXTINTOR TIPO CO2 AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.20mx0.30m)</t>
-  </si>
-  <si>
-    <t>03.01.12.02.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SEÑAL PULSADOR DE ALARMA CONTRA INCENDIO AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.20mx0.30m)</t>
-  </si>
-  <si>
-    <t>03.01.12.02.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SEÑAL AVISADOR SONORO AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.20mx0.30m)</t>
-  </si>
-  <si>
-    <t>03.01.12.02.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SEÑAL PROHIBIDO FUMAR AUTOADHESIVA SOBRE BASE CELTEX 2mm (0.60mx0.30m)</t>
-  </si>
-  <si>
-    <t>03.01.12.02.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SEÑAL PROHIBIDO EL PASO A PERSONAL NO AUTORIZADO AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE ACRILICO EXTERIOR 2mm (0.20mx0</t>
-  </si>
-  <si>
-    <t>03.01.12.02.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SEÑAL ATENCION RIESGO ELECTRICO AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.20mx0.30m)</t>
-  </si>
-  <si>
-    <t>03.01.12.02.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SEÑAL CARTEL PARA INDICAR EL AFORO DE AMBIENTE AUTOADHESIVA SOBRE BASE CELTEX 2mm (0.30mx0.20m)</t>
-  </si>
-  <si>
-    <t>03.01.12.02.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SEÑAL CARTEL PARA INDICAR EL USO OBLIGATORIO DE EPP AUTOADHESIVA SOBRE BASE CELTEX 2mm (0.30mx0.20m)</t>
-  </si>
-  <si>
-    <t>03.01.12.02.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SEÑAL REFLECTIVA DE ALUMINIO PUNTO DE REUNION EN CASO DE EMERGENCIA 5mm (0.60mx0.90m) SOBRE POSTE FE Ø2" 2.5m INC TORNILLOS DE FIJACION</t>
-  </si>
-  <si>
-    <t>03.01.12.02.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            SEÑAL DE ZONA DE SEGURIDAD EXTERNA PINTADA EN PISO DE ALTO TRANSITO COLOR VERDE</t>
-  </si>
-  <si>
-    <t>03.01.12.03</t>
-  </si>
-  <si>
-    <t>03.01.12.03.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            EXTINTOR TIPO PQS (POLVO QUIMICO SECO) - 20 LB</t>
-  </si>
-  <si>
-    <t>03.01.12.03.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            EXTINTOR TIPO CO2 (DIOXIDO DE CARBONO) - 15 LB</t>
+    <t>VARIOS</t>
+  </si>
+  <si>
+    <t>MUROS Y TABIQUES DE ALBAÑILERIA</t>
+  </si>
+  <si>
+    <t>MUROS DE LADRILLO KING KONG DE ARCILLA</t>
+  </si>
+  <si>
+    <t>MURO LADRILLO KK TIPO IV MEZCLA 1:5, JUNTAS 1.5cm DE SOGA</t>
+  </si>
+  <si>
+    <t>MUROS DE LADRILLO CALCAREO</t>
+  </si>
+  <si>
+    <t>MURO LADRILLO SILICO CALCAREO MEZCLA 1:5, JUNTAS 1.5cm DE SOGA</t>
+  </si>
+  <si>
+    <t>MUROS CON EL SISTEMA DE CONSTRUCCION EN SECO (SISTEMA DRYWALL O SIMILAR)</t>
+  </si>
+  <si>
+    <t>TABIQUERIA DE DRYWALL INCLUYE PARANTES Y RIELES</t>
+  </si>
+  <si>
+    <t>TABIQUERIA DE DRYWALL RESISTENTE AL FUEGO INCLUYE RIELES Y PARANTES</t>
+  </si>
+  <si>
+    <t>VIGAS DE FIBROCEMENTO INCLUYE RIELES Y PARANTES</t>
+  </si>
+  <si>
+    <t>REVOQUES Y REVESTIMIENTOS</t>
+  </si>
+  <si>
+    <t>TARRAJEO RAYADO PRIMARIO</t>
+  </si>
+  <si>
+    <t>TARRAJEO PRIMARIO Y RAYADO C/ MEZCLA 1:5 E=1.5cm</t>
+  </si>
+  <si>
+    <t>TARRAJEO EN INTERIORES</t>
+  </si>
+  <si>
+    <t>TARRAJEO DE MUROS INTERIORES FROTACHADO CON MEZ. C:A 1:5, E=1.5cm</t>
+  </si>
+  <si>
+    <t>TARRAJEO DE PLACAS MEZ. C:A 1:5, E=1.5cm.</t>
+  </si>
+  <si>
+    <t>TARRAJEO DE COLUMNAS MEZ. C:A 1:5, E=1.5 CM.</t>
+  </si>
+  <si>
+    <t>TARRAJEO DE VIGAS MEZLA C:A 1:5, E=1.5 CM.</t>
+  </si>
+  <si>
+    <t>TARRAJEO EN EXTERIORES</t>
+  </si>
+  <si>
+    <t>TARRAJEO DE MUROS EXTERIORES, MEZCLA C:A 1:5, E=1.5cm</t>
+  </si>
+  <si>
+    <t>VESTIDURA DE DERRAMES</t>
+  </si>
+  <si>
+    <t>VESTIDURA DE DERRAMES A=0.15m, MEZCLA C:A 1:5 E=1.5cm</t>
+  </si>
+  <si>
+    <t>BRUÑAS</t>
+  </si>
+  <si>
+    <t>BRUÑAS 1cm x 1cm</t>
+  </si>
+  <si>
+    <t>TARRAJEO EN FONDO DE ESCALERA</t>
+  </si>
+  <si>
+    <t>TARRAJEO EN FONDO EN ESCALERA, E=1.5cm. C:A 1:5</t>
+  </si>
+  <si>
+    <t>REVESTIMIENTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVESTIMIENTO DE TABLERO DE CONCRETO CON CERAMICO 0.30X0.30m    </t>
+  </si>
+  <si>
+    <t>03.01.02.07.02</t>
+  </si>
+  <si>
+    <t>REVESTIMIENTO DE SARDINEL CON CERAMICO ANTIDESLIZANTE 0.30x0.30m</t>
+  </si>
+  <si>
+    <t>VESTIDURA DE FONDO DE TABLERO</t>
+  </si>
+  <si>
+    <t>REVESTIMIENTO DE CEMENTO SEMIPULIDO EN BANCA DE CONCRETO</t>
+  </si>
+  <si>
+    <t>CIELORRASOS</t>
+  </si>
+  <si>
+    <t>FALSO CIELORRASO</t>
+  </si>
+  <si>
+    <t>03.01.03.01.01</t>
+  </si>
+  <si>
+    <t>FALSO CIELO RASO CON BALDOSA  RESISTENTE A LA HUMEDAD DE 0.60mx0.60m.</t>
+  </si>
+  <si>
+    <t>PISOS Y PAVIMENTOS</t>
+  </si>
+  <si>
+    <t>CONTRAPISOS</t>
+  </si>
+  <si>
+    <t>03.01.04.01.01</t>
+  </si>
+  <si>
+    <t>CONTRAPISO DE CEMENTO 37mm, MEZCLA 1:5</t>
+  </si>
+  <si>
+    <t>PISOS</t>
+  </si>
+  <si>
+    <t>03.01.04.02.01</t>
+  </si>
+  <si>
+    <t>PISOS DE CERAMICO</t>
+  </si>
+  <si>
+    <t>03.01.04.02.01.01</t>
+  </si>
+  <si>
+    <t>PISO DE CERAMICO ALTO TRANSITO PEI-IV, 30cm x 30cm</t>
+  </si>
+  <si>
+    <t>PISOS EN PISTA ATLETICA</t>
+  </si>
+  <si>
+    <t>CONFORMACION Y COMPACTACION A NIVEL DE SUBRASANTE C/EQUIPO</t>
+  </si>
+  <si>
+    <t>03.01.04.02.02.02</t>
+  </si>
+  <si>
+    <t>BASE GRANULAR e=0.20 m.</t>
+  </si>
+  <si>
+    <t>03.01.04.02.02.03</t>
+  </si>
+  <si>
+    <t>IMPRIMACION ASFALTICA</t>
+  </si>
+  <si>
+    <t>03.01.04.02.02.04</t>
+  </si>
+  <si>
+    <t>CARPETA ASFALTICA EN CALIENTE e = 2"</t>
+  </si>
+  <si>
+    <t>03.01.04.02.02.05</t>
+  </si>
+  <si>
+    <t>RIEGO DE LIGA</t>
+  </si>
+  <si>
+    <t>03.01.04.02.02.06</t>
+  </si>
+  <si>
+    <t>CARPETA ASFALTICA EN CALIENTE e=3cm</t>
+  </si>
+  <si>
+    <t>03.01.04.02.02.07</t>
+  </si>
+  <si>
+    <t>PISTA ATLETICA SISTEMA SPRAY e=13mm</t>
+  </si>
+  <si>
+    <t>03.01.04.02.02.08</t>
+  </si>
+  <si>
+    <t>DEMARCACION DE PISTA ATLETICA</t>
+  </si>
+  <si>
+    <t>03.01.04.02.03</t>
+  </si>
+  <si>
+    <t>PISOS DE GRASS</t>
+  </si>
+  <si>
+    <t>03.01.04.02.03.01</t>
+  </si>
+  <si>
+    <t>PREPARACION DE TERRENO</t>
+  </si>
+  <si>
+    <t>03.01.04.02.03.02</t>
+  </si>
+  <si>
+    <t>NIVELACION A NIVEL DE RASANTE C/MAQ.</t>
+  </si>
+  <si>
+    <t>03.01.04.02.03.03</t>
+  </si>
+  <si>
+    <t>COMPACTADO CON RODILLO MANUAL</t>
+  </si>
+  <si>
+    <t>03.01.04.02.03.04</t>
+  </si>
+  <si>
+    <t>SIEMBRA DE GRAS BERMUDA INC RASTRILLADO Y RULADO</t>
+  </si>
+  <si>
+    <t>03.01.04.02.03.05</t>
+  </si>
+  <si>
+    <t>FERTILIZACION DEL SUELO</t>
+  </si>
+  <si>
+    <t>03.01.04.02.03.06</t>
+  </si>
+  <si>
+    <t>MANTENIMIENTO DE GRAS POR 30 DIAS</t>
+  </si>
+  <si>
+    <t>03.01.04.02.03.07</t>
+  </si>
+  <si>
+    <t>PINTURA  DE DEMARCACION EN CAMPO</t>
+  </si>
+  <si>
+    <t>03.01.04.02.03.08</t>
+  </si>
+  <si>
+    <t>REFINE Y NIVELADO DE TERRENO</t>
+  </si>
+  <si>
+    <t>03.01.04.02.03.09</t>
+  </si>
+  <si>
+    <t>SEMBRADO DE GRASS INC. TIERRA DE CHACRA</t>
+  </si>
+  <si>
+    <t>PISOS DE CEMENTO</t>
+  </si>
+  <si>
+    <t>PISO DE CEMENTO PULIDO Y BRUÑADO @1m</t>
+  </si>
+  <si>
+    <t>03.01.04.02.04.02</t>
+  </si>
+  <si>
+    <t>VEREDA DE CONCRETO F'C=175 KG/CM2 E=0.10M EN VEREDA, ACABADO SEMIPULIDO CON BRUÑAS @1.00 m</t>
+  </si>
+  <si>
+    <t>SARDINELES</t>
+  </si>
+  <si>
+    <t>SARDINEL DE CONCRETO PARA DUCHAS (ANCHO=0.08m, ALTURA=0.10m)</t>
+  </si>
+  <si>
+    <t>ZOCALOS Y CONTRAZOCALOS</t>
+  </si>
+  <si>
+    <t>ZOCALOS</t>
+  </si>
+  <si>
+    <t>03.01.05.01.01</t>
+  </si>
+  <si>
+    <t>ZOCALO DE CERAMICO</t>
+  </si>
+  <si>
+    <t>03.01.05.01.01.01</t>
+  </si>
+  <si>
+    <t>ZOCALO DE CERAMICO 30cm x 30cm, h=1.80m</t>
+  </si>
+  <si>
+    <t>CONTRAZOCALOS</t>
+  </si>
+  <si>
+    <t>03.01.05.02.01</t>
+  </si>
+  <si>
+    <t>CONTRAZOCALO DE CEMENTO</t>
+  </si>
+  <si>
+    <t>03.01.05.02.01.01</t>
+  </si>
+  <si>
+    <t>CONTRAZOCALO DE CEMENTO PULIDO; H = 0.10m, MEZCLA 1:5</t>
+  </si>
+  <si>
+    <t>03.01.06</t>
+  </si>
+  <si>
+    <t>CARPINTERIA DE MADERA</t>
+  </si>
+  <si>
+    <t>03.01.06.01</t>
+  </si>
+  <si>
+    <t>PUERTAS DE MADERA</t>
+  </si>
+  <si>
+    <t>03.01.06.01.01</t>
+  </si>
+  <si>
+    <t>PUERTA APANELADA  MADERA TORNILLO 2"x5", (1 HOJA); INC MARCO  Y ACC FIJACION, B08-PA01 (1.00mx2.60m)</t>
+  </si>
+  <si>
+    <t>03.01.06.01.02</t>
+  </si>
+  <si>
+    <t>PUERTA APANELADA  MADERA TORNILLO 2"x5", (1 HOJA); INC MARCO  Y ACC FIJACION, B08-PA02 (0.90mx2.60m)</t>
+  </si>
+  <si>
+    <t>03.01.06.02</t>
+  </si>
+  <si>
+    <t>DIVISIONES PARA SERVICIOS HIGIENICOS</t>
+  </si>
+  <si>
+    <t>03.01.06.02.01</t>
+  </si>
+  <si>
+    <t>DIVISIONES DE TABLERO MELAMINICO e= 18 mm EN SS.HH.; INCL. ESTRUCTURA DE TUBULAR DE ALUMINIO 1 1/2" X 1 1/2" Y ACC H=1.80m, INCLUYE PUERTAS Y ACCESORIOS.</t>
+  </si>
+  <si>
+    <t>03.01.06.02.02</t>
+  </si>
+  <si>
+    <t>DIVISIONES DE TABLERO MELAMINICO e= 18 mm EN URINARIOS.; INCL. ACCESORIOS L=0.40m, H=0.75m</t>
+  </si>
+  <si>
+    <t>CARPINTERIA METALICA Y HERRERIA</t>
+  </si>
+  <si>
+    <t>PUERTAS METALICAS</t>
+  </si>
+  <si>
+    <t>03.01.07.01.01</t>
+  </si>
+  <si>
+    <t>PUERTA DE ACERO GALV. C/MARCO, CERTIFICACION UL, ACC FIJACION (1 HOJA), B08-PCF01 (1.00mx2.10m)</t>
+  </si>
+  <si>
+    <t>VENTANAS DE ALUMINIO</t>
+  </si>
+  <si>
+    <t>VENTANA ALTA DE ALUMINIO SISTEMA PIVOT, CON VIDRIO TEMPLADO INCOLORO DE 6mm, INC.ACCESORIOS</t>
+  </si>
+  <si>
+    <t>03.01.07.03</t>
+  </si>
+  <si>
+    <t>BARANDAS METALICAS</t>
+  </si>
+  <si>
+    <t>03.01.07.03.01</t>
+  </si>
+  <si>
+    <t>BARANDA DE TUBO DE FIERRO NEGRO Ø 2" e=1.5mm Y Ø 1" e=1.5mm, C/ PARANTE Ø 1 1/2" e=1.5mm, H = 1.00m, INC ACC Y ACAB SATINADO BASE ZINCROMATO, ANTICORROSIVO Y PINTURA ESMALTE</t>
+  </si>
+  <si>
+    <t>03.01.07.04</t>
+  </si>
+  <si>
+    <t>PASAMANOS METALICOS</t>
+  </si>
+  <si>
+    <t>03.01.07.04.01</t>
+  </si>
+  <si>
+    <t>PASAMANOS DE TUBO DE FIERRO NEGRO Ø 2" e=1.5mm, IN ACC Y ACAB SATINADO BASE ZINCROMATO, ANTICORROSIVO Y PINTURA ESMALTE</t>
+  </si>
+  <si>
+    <t>03.01.07.05</t>
+  </si>
+  <si>
+    <t>ELEMENTOS METALICOS ESPECIALES</t>
+  </si>
+  <si>
+    <t>03.01.07.05.01</t>
+  </si>
+  <si>
+    <t>PLATINA DE ALUMINIO EN CAMBIO DE ACABADOS DE PISO</t>
+  </si>
+  <si>
+    <t>03.01.07.05.02</t>
+  </si>
+  <si>
+    <t>JAULA PARA LANZAMIENTO DE MARTILLO Y DISCO</t>
+  </si>
+  <si>
+    <t>CERRAJERIA</t>
+  </si>
+  <si>
+    <t>CERRADURAS</t>
+  </si>
+  <si>
+    <t>03.01.08.01.01</t>
+  </si>
+  <si>
+    <t>CERRADURA CON MANIJA TIPO PALANCA PARA PUERTAS DE MADERA CONTRAPLACADA</t>
+  </si>
+  <si>
+    <t>03.01.08.01.02</t>
+  </si>
+  <si>
+    <t>CERRADURA CERTIFICACION UL CON UN PUNTO DE CIERRE + MANIJA EXTERIOR E INTERIOR</t>
+  </si>
+  <si>
+    <t>03.01.08.02</t>
+  </si>
+  <si>
+    <t>BISAGRAS</t>
+  </si>
+  <si>
+    <t>03.01.08.02.01</t>
+  </si>
+  <si>
+    <t>BISAGRA T2- SET 4 BISAGRAS CAPUCHINAS ALUMINIZADAS 4"x4" INC TORNILLOS FIJACIÓN</t>
+  </si>
+  <si>
+    <t>PINTURA</t>
+  </si>
+  <si>
+    <t>PINTURA DE CIELORRASOS, VIGAS</t>
+  </si>
+  <si>
+    <t>PINTURA DE CIELORRASOS Y VIGAS CON IMPRIMANTE Y ACABADO LATEX (2 MANOS)</t>
+  </si>
+  <si>
+    <t>PINTURA DE MUROS INTERIORES, COLUMNAS, MUROS DE CONCRETO Y PLACAS</t>
+  </si>
+  <si>
+    <t>PINTURA DE MUROS INTERIORES CON IMPRIMANTE Y ACABADO LATEX (2 MANOS)</t>
+  </si>
+  <si>
+    <t>03.01.09.02.02</t>
+  </si>
+  <si>
+    <t>PINTURA DE MUROS DE DRYWALL O FIBROCEMENTO  ACABADO LATEX (2 MANOS)</t>
+  </si>
+  <si>
+    <t>03.01.09.03</t>
+  </si>
+  <si>
+    <t>PINTURA DE MUROS EXTERIORES</t>
+  </si>
+  <si>
+    <t>03.01.09.03.01</t>
+  </si>
+  <si>
+    <t>PINTURA DE MUROS EXTERIORES CON IMPRIMANTE Y ACABADO LATEX (2 MANOS)</t>
+  </si>
+  <si>
+    <t>03.01.09.03.02</t>
+  </si>
+  <si>
+    <t>PINTURA DE DERRAME CON IMPRIMANTE Y ACABADO LATEX (2 MANOS)</t>
+  </si>
+  <si>
+    <t>03.01.09.04</t>
+  </si>
+  <si>
+    <t>PINTURA VARIOS</t>
+  </si>
+  <si>
+    <t>03.01.09.04.01</t>
+  </si>
+  <si>
+    <t>PINTURA EN PISO PARA SEÑAL DE DISCAPACITADOS Y SILLA C/PINTURA DE TRANSITO BLANCO 1.50x1.50m</t>
+  </si>
+  <si>
+    <t>VARIOS, LIMPIEZA, JARDINERIA</t>
+  </si>
+  <si>
+    <t>03.01.10.01</t>
+  </si>
+  <si>
+    <t>03.01.10.01.01</t>
+  </si>
+  <si>
+    <t>TABLERO DE CONCRETO e=0.08m</t>
+  </si>
+  <si>
+    <t>03.01.10.01.02</t>
+  </si>
+  <si>
+    <t>JUNTAS DE CONSTRUCCION</t>
+  </si>
+  <si>
+    <t>03.01.10.01.03</t>
+  </si>
+  <si>
+    <t>SOLAQUEO LADO VERTICAL DE GRADERIAS</t>
+  </si>
+  <si>
+    <t>SEÑALIZACION Y SEGURIDAD</t>
+  </si>
+  <si>
+    <t>SEÑAL ORIENTATIVA - INDICATIVA</t>
+  </si>
+  <si>
+    <t>03.01.11.01.01</t>
+  </si>
+  <si>
+    <t>T.01 IDENTIFICATIVO ADOSADO DE 0.45mx0.60m</t>
+  </si>
+  <si>
+    <t>03.01.11.01.02</t>
+  </si>
+  <si>
+    <t>T.02 IDENTIFICATIVO ADOSADO DE 0.15mx0.30m</t>
+  </si>
+  <si>
+    <t>03.01.11.02</t>
+  </si>
+  <si>
+    <t>SEÑAL DE SEGURIDAD</t>
+  </si>
+  <si>
+    <t>03.01.11.02.01</t>
+  </si>
+  <si>
+    <t>SEÑAL ACCESO DE SALIDA AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.30mx0.20m)</t>
+  </si>
+  <si>
+    <t>03.01.11.02.02</t>
+  </si>
+  <si>
+    <t>SEÑAL DIRECCION EN SENTIDO DE EVACUACION AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 3mm (0.20mx0.30m)</t>
+  </si>
+  <si>
+    <t>03.01.11.02.03</t>
+  </si>
+  <si>
+    <t>SEÑAL SUBIR-BAJAR ESCALERA AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.20mx0.30m)</t>
+  </si>
+  <si>
+    <t>03.01.11.02.04</t>
+  </si>
+  <si>
+    <t>SEÑAL PUERTA CORTAFUEGO AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.20mx0.30m)</t>
+  </si>
+  <si>
+    <t>03.01.11.02.05</t>
+  </si>
+  <si>
+    <t>SEÑAL EXTINTOR TIPO PQS AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.20mx0.30m)</t>
+  </si>
+  <si>
+    <t>03.01.11.02.06</t>
+  </si>
+  <si>
+    <t>SEÑAL EXTINTOR TIPO CO2 AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.20mx0.30m)</t>
+  </si>
+  <si>
+    <t>03.01.11.02.07</t>
+  </si>
+  <si>
+    <t>SEÑAL PULSADOR DE ALARMA CONTRA INCENDIO AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.20mx0.30m)</t>
+  </si>
+  <si>
+    <t>03.01.11.02.08</t>
+  </si>
+  <si>
+    <t>SEÑAL AVISADOR SONORO AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.20mx0.30m)</t>
+  </si>
+  <si>
+    <t>03.01.11.02.09</t>
+  </si>
+  <si>
+    <t>SEÑAL PROHIBIDO FUMAR AUTOADHESIVA SOBRE BASE CELTEX 2mm (0.60mx0.30m)</t>
+  </si>
+  <si>
+    <t>03.01.11.02.10</t>
+  </si>
+  <si>
+    <t>SEÑAL PROHIBIDO EL PASO A PERSONAL NO AUTORIZADO AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE ACRILICO EXTERIOR 2mm (0.20mx0</t>
+  </si>
+  <si>
+    <t>03.01.11.02.11</t>
+  </si>
+  <si>
+    <t>SEÑAL ATENCION RIESGO ELECTRICO AUTOADHESIVA FOTOLUMINISCENTE SOBRE BASE CELTEX 2mm (0.20mx0.30m)</t>
+  </si>
+  <si>
+    <t>03.01.11.02.12</t>
+  </si>
+  <si>
+    <t>SEÑAL CARTEL PARA INDICAR EL AFORO DE AMBIENTE AUTOADHESIVA SOBRE BASE CELTEX 2mm (0.30mx0.20m)</t>
+  </si>
+  <si>
+    <t>03.01.11.02.13</t>
+  </si>
+  <si>
+    <t>SEÑAL CARTEL PARA INDICAR EL USO OBLIGATORIO DE EPP AUTOADHESIVA SOBRE BASE CELTEX 2mm (0.30mx0.20m)</t>
+  </si>
+  <si>
+    <t>03.01.11.02.14</t>
+  </si>
+  <si>
+    <t>SEÑAL REFLECTIVA DE ALUMINIO PUNTO DE REUNION EN CASO DE EMERGENCIA 5mm (0.60mx0.90m) SOBRE POSTE FE Ø2" 2.5m INC TORNILLOS DE FIJACION</t>
+  </si>
+  <si>
+    <t>03.01.11.02.15</t>
+  </si>
+  <si>
+    <t>SEÑAL DE ZONA DE SEGURIDAD EXTERNA PINTADA EN PISO DE ALTO TRANSITO COLOR VERDE</t>
+  </si>
+  <si>
+    <t>03.01.11.03</t>
+  </si>
+  <si>
+    <t>03.01.11.03.01</t>
+  </si>
+  <si>
+    <t>EXTINTOR TIPO PQS (POLVO QUIMICO SECO) - 20 LB</t>
+  </si>
+  <si>
+    <t>03.01.11.03.02</t>
+  </si>
+  <si>
+    <t>EXTINTOR TIPO CO2 (DIOXIDO DE CARBONO) - 15 LB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -820,6 +917,25 @@
       <sz val="9"/>
       <color rgb="FFFF00FF"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="ARIAL"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color indexed="8"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color indexed="8"/>
+      <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -900,10 +1016,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -929,9 +1048,34 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{70E1D809-113A-4826-B414-552776C5C452}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1261,17 +1405,39 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="613" row="6">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{A2D4D6A7-DB00-4561-804B-CA1C53560F8F}">
+  <we:reference id="wa200010725" version="1.0.0.1" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010725" version="1.0.0.1" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;df4f01a0-d8e9-4b96-9756-284564243a1e&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D494C7E0-CCBE-4C04-AAF4-9C2F438F6C3D}">
   <dimension ref="A1:C136"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" customWidth="1"/>
-    <col min="2" max="2" width="96.44140625" customWidth="1"/>
-    <col min="3" max="3" width="4.77734375" customWidth="1"/>
+    <col min="1" max="1" width="19.53515625" customWidth="1"/>
+    <col min="2" max="2" width="96.4609375" customWidth="1"/>
+    <col min="3" max="3" width="4.765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1280,7 +1446,7 @@
       </c>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1289,1317 +1455,2782 @@
       </c>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3"/>
-    </row>
-    <row r="4" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="B4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B5" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="B6" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B7" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="B8" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B9" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="B10" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B11" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="B12" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B13" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+      <c r="B14" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+      <c r="B16" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B17" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="B18" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B19" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="B20" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B21" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="B22" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B23" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+    </row>
+    <row r="24" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B24" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
-        <v>52</v>
-      </c>
       <c r="B25" s="11" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="8" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="10" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="8" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="10" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="10" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="10" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="10" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="6" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="8" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="10" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="6" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="8" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="10" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="8" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="13" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C40" s="3"/>
     </row>
-    <row r="41" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="10" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="13" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="C42" s="3"/>
     </row>
-    <row r="43" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="15"/>
+    <row r="43" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="15" t="s">
+        <v>43</v>
+      </c>
       <c r="B43" s="11" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="15"/>
+    <row r="44" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="15" t="s">
+        <v>112</v>
+      </c>
       <c r="B44" s="11" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="15"/>
+    <row r="45" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="15" t="s">
+        <v>114</v>
+      </c>
       <c r="B45" s="11" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="15"/>
+    <row r="46" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="15" t="s">
+        <v>116</v>
+      </c>
       <c r="B46" s="11" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="15"/>
+    <row r="47" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="B47" s="11" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="15"/>
+    <row r="48" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="15" t="s">
+        <v>120</v>
+      </c>
       <c r="B48" s="11" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="15"/>
+    <row r="49" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="15" t="s">
+        <v>122</v>
+      </c>
       <c r="B49" s="11" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="15"/>
+    <row r="50" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="15" t="s">
+        <v>124</v>
+      </c>
       <c r="B50" s="11" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="13" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="C51" s="3"/>
     </row>
-    <row r="52" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="15"/>
+    <row r="52" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="B52" s="11" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="15"/>
+    <row r="53" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="15" t="s">
+        <v>130</v>
+      </c>
       <c r="B53" s="11" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="15"/>
+    <row r="54" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="15" t="s">
+        <v>132</v>
+      </c>
       <c r="B54" s="11" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="15"/>
+    <row r="55" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="15" t="s">
+        <v>134</v>
+      </c>
       <c r="B55" s="11" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="15"/>
+    <row r="56" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="15" t="s">
+        <v>136</v>
+      </c>
       <c r="B56" s="11" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="15"/>
+    <row r="57" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="15" t="s">
+        <v>138</v>
+      </c>
       <c r="B57" s="11" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="15"/>
+    <row r="58" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="15" t="s">
+        <v>140</v>
+      </c>
       <c r="B58" s="11" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="15"/>
+    <row r="59" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="15" t="s">
+        <v>142</v>
+      </c>
       <c r="B59" s="11" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="15"/>
+    <row r="60" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="15" t="s">
+        <v>144</v>
+      </c>
       <c r="B60" s="11" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="13" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="C61" s="3"/>
     </row>
-    <row r="62" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="10" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C62" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="15"/>
+    <row r="63" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="15" t="s">
+        <v>148</v>
+      </c>
       <c r="B63" s="11" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="13" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="C64" s="3"/>
     </row>
-    <row r="65" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="10" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="6" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="C66" s="3"/>
     </row>
-    <row r="67" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="8" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="C67" s="3"/>
     </row>
-    <row r="68" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="13" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="C68" s="3"/>
     </row>
-    <row r="69" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="10" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="8" t="s">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="C70" s="3"/>
     </row>
-    <row r="71" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="13" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="C71" s="3"/>
     </row>
-    <row r="72" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="10" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="C72" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="6" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="C73" s="3"/>
     </row>
-    <row r="74" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="8" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="C74" s="3"/>
     </row>
-    <row r="75" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="15"/>
+    <row r="75" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="15" t="s">
+        <v>167</v>
+      </c>
       <c r="B75" s="11" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="C75" s="12" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="15"/>
+    <row r="76" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="15" t="s">
+        <v>169</v>
+      </c>
       <c r="B76" s="11" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="C76" s="12" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="8" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="C77" s="3"/>
     </row>
-    <row r="78" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="10" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="C78" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="10" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="6" t="s">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="C80" s="3"/>
     </row>
-    <row r="81" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="8" t="s">
-        <v>143</v>
+        <v>52</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="C81" s="3"/>
     </row>
-    <row r="82" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="15"/>
+    <row r="82" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="15" t="s">
+        <v>179</v>
+      </c>
       <c r="B82" s="11" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="8" t="s">
-        <v>146</v>
+        <v>53</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="C83" s="3"/>
     </row>
-    <row r="84" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="15"/>
+    <row r="84" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="15" t="s">
+        <v>54</v>
+      </c>
       <c r="B84" s="11" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="C84" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="8" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="C85" s="3"/>
     </row>
-    <row r="86" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="15"/>
+    <row r="86" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="15" t="s">
+        <v>185</v>
+      </c>
       <c r="B86" s="11" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="C86" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="8" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="C87" s="3"/>
     </row>
-    <row r="88" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="10" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="C88" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="8" t="s">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="C89" s="3"/>
     </row>
-    <row r="90" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="10" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="C90" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="15"/>
+    <row r="91" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="15" t="s">
+        <v>195</v>
+      </c>
       <c r="B91" s="11" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="C91" s="12" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="6" t="s">
-        <v>161</v>
+        <v>55</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="C92" s="3"/>
     </row>
-    <row r="93" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="8" t="s">
-        <v>163</v>
+        <v>56</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="C93" s="3"/>
     </row>
-    <row r="94" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="10" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="C94" s="12" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="15"/>
+    <row r="95" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A95" s="15" t="s">
+        <v>201</v>
+      </c>
       <c r="B95" s="11" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="C95" s="12" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="8" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="C96" s="3"/>
     </row>
-    <row r="97" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="10" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="C97" s="12" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="6" t="s">
-        <v>172</v>
+        <v>57</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="C98" s="3"/>
     </row>
-    <row r="99" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="8" t="s">
-        <v>174</v>
+        <v>58</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="C99" s="3"/>
     </row>
-    <row r="100" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="10" t="s">
-        <v>176</v>
+        <v>59</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="C100" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="8" t="s">
-        <v>178</v>
+        <v>60</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="C101" s="3"/>
     </row>
-    <row r="102" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="10" t="s">
-        <v>180</v>
+        <v>61</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="C102" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="15"/>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A103" s="15" t="s">
+        <v>212</v>
+      </c>
       <c r="B103" s="11" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="C103" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A104" s="8" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="C104" s="3"/>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A105" s="10" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="15"/>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A106" s="15" t="s">
+        <v>218</v>
+      </c>
       <c r="B106" s="11" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="C106" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A107" s="8" t="s">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>188</v>
+        <v>221</v>
       </c>
       <c r="C107" s="3"/>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="15"/>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A108" s="15" t="s">
+        <v>222</v>
+      </c>
       <c r="B108" s="11" t="s">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="C108" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A109" s="6" t="s">
-        <v>190</v>
+        <v>62</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="C109" s="3"/>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A110" s="8" t="s">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>193</v>
+        <v>65</v>
       </c>
       <c r="C110" s="3"/>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A111" s="10" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="C111" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" s="15"/>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A112" s="15" t="s">
+        <v>228</v>
+      </c>
       <c r="B112" s="11" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="C112" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" s="15"/>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A113" s="15" t="s">
+        <v>230</v>
+      </c>
       <c r="B113" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A114" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C114" s="3"/>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A115" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="C115" s="3"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A116" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A117" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A118" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C118" s="3"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A119" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A120" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A121" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="B121" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A122" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B122" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A123" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B123" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A124" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="B124" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A125" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B125" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A126" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="B126" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C126" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A127" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B127" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A128" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="B128" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A129" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="B129" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A130" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="B130" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A131" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="B131" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A132" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B132" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A133" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="B133" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A134" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B134" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C134" s="3"/>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A135" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="B135" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A136" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="B136" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="C136" s="18" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4A9A0F-70AE-4B0B-B942-0BD30AF13A22}">
+  <dimension ref="A1:C136"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="80.23046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="20"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="20"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="20"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="20"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="20"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="20"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="20"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="20"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="20"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A21" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="20"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="20"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A26" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="20"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="20"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A31" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="20"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" s="20"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" s="20"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="20"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" s="20"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40" s="20"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="20"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A43" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A44" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A45" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A46" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A47" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A48" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A49" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A50" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A51" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" s="20"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A52" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A53" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A54" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A55" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A56" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A57" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A58" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A59" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A60" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B60" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A61" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="C61" s="20"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A62" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="C62" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A63" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A64" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="C64" s="20"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A65" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B65" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="C65" s="21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A66" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B66" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="C66" s="20"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A67" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B67" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" s="20"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A68" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="B68" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C68" s="20"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A69" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B69" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A70" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B70" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="C70" s="20"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A71" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B71" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C71" s="20"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A72" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B72" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="C72" s="21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A73" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B73" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="C73" s="20"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A74" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="C74" s="20"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A75" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C75" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A76" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A77" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B77" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="C77" s="20"/>
+    </row>
+    <row r="78" spans="1:3" ht="14.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A79" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="B79" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A80" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B80" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="C80" s="20"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A81" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B81" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="C81" s="20"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A82" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A83" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B83" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="C83" s="20"/>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A84" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A85" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="B85" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C85" s="20"/>
+    </row>
+    <row r="86" spans="1:3" ht="14.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="C86" s="21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A87" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="B87" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="C87" s="20"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A88" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="B88" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C88" s="21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A89" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="B89" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="C89" s="20"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A90" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B90" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="C90" s="21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A91" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="B91" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="C91" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A92" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B92" s="22" t="s">
         <v>197</v>
       </c>
-      <c r="C113" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" s="6" t="s">
+      <c r="C92" s="20"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A93" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B93" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="B114" s="7" t="s">
+      <c r="C93" s="20"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A94" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="C114" s="3"/>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" s="8" t="s">
+      <c r="B94" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="B115" s="9" t="s">
+      <c r="C94" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A95" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="C115" s="3"/>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" s="10" t="s">
+      <c r="B95" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="B116" s="11" t="s">
+      <c r="C95" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A96" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="C116" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" s="10" t="s">
+      <c r="B96" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="B117" s="11" t="s">
+      <c r="C96" s="20"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A97" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="C117" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="8" t="s">
+      <c r="B97" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="B118" s="9" t="s">
+      <c r="C97" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A98" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B98" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="C118" s="3"/>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="10" t="s">
+      <c r="C98" s="20"/>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A99" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B99" s="22" t="s">
         <v>208</v>
       </c>
-      <c r="B119" s="11" t="s">
+      <c r="C99" s="20"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A100" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B100" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C119" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="10" t="s">
+      <c r="C100" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A101" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B101" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B120" s="11" t="s">
+      <c r="C101" s="20"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A102" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B102" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="C120" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="10" t="s">
+      <c r="C102" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A103" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="B121" s="11" t="s">
+      <c r="B103" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="C121" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="10" t="s">
+      <c r="C103" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A104" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="B122" s="11" t="s">
+      <c r="B104" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="C122" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" s="10" t="s">
+      <c r="C104" s="20"/>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A105" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="B123" s="11" t="s">
+      <c r="B105" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="C123" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" s="10" t="s">
+      <c r="C105" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A106" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="B124" s="11" t="s">
+      <c r="B106" s="23" t="s">
         <v>219</v>
       </c>
-      <c r="C124" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="10" t="s">
+      <c r="C106" s="21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A107" s="21" t="s">
         <v>220</v>
       </c>
-      <c r="B125" s="11" t="s">
+      <c r="B107" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="C125" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" s="10" t="s">
+      <c r="C107" s="20"/>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A108" s="21" t="s">
         <v>222</v>
       </c>
-      <c r="B126" s="11" t="s">
+      <c r="B108" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C126" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="10" t="s">
+      <c r="C108" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A109" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B109" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="B127" s="11" t="s">
+      <c r="C109" s="20"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A110" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="C127" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" s="10" t="s">
+      <c r="B110" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C110" s="20"/>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A111" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B128" s="11" t="s">
+      <c r="B111" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="C128" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" s="10" t="s">
+      <c r="C111" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A112" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="B129" s="11" t="s">
+      <c r="B112" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="C129" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" s="10" t="s">
+      <c r="C112" s="21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A113" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="B130" s="11" t="s">
+      <c r="B113" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="C130" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" s="10" t="s">
+      <c r="C113" s="21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A114" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B114" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="B131" s="11" t="s">
+      <c r="C114" s="20"/>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A115" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B115" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="C131" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" s="10" t="s">
+      <c r="C115" s="20"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A116" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="B132" s="11" t="s">
+      <c r="B116" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="C132" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" s="10" t="s">
+      <c r="C116" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A117" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="B133" s="11" t="s">
+      <c r="B117" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="C133" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" s="8" t="s">
+      <c r="C117" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A118" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="B134" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="C134" s="3"/>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" s="10" t="s">
+      <c r="B118" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="B135" s="11" t="s">
+      <c r="C118" s="20"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A119" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="C135" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="16" t="s">
+      <c r="B119" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="B136" s="17" t="s">
+      <c r="C119" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A120" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="C136" s="18" t="s">
+      <c r="B120" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="C120" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A121" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="B121" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="C121" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A122" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="B122" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="C122" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A123" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="B123" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="C123" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A124" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="C124" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A125" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="C125" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A126" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="C126" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A127" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="B127" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="C127" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A128" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="B128" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="C128" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A129" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="B129" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="C129" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A130" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="B130" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="C130" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A131" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="B131" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="C131" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A132" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="B132" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="C132" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A133" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="B133" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="C133" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A134" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="B134" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C134" s="20"/>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A135" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="B135" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="C135" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A136" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="B136" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="C136" s="21" t="s">
         <v>0</v>
       </c>
     </row>
